--- a/Datasets/vjcortesa_Presurvey_questions overview.xlsx
+++ b/Datasets/vjcortesa_Presurvey_questions overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/jcortesarevalo_tudelft_nl/Documents/Documents/TUDelft/18_Game Data Analysis/R data analysis BEPs/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1117" documentId="11_F25DC773A252ABDACC10482FB9DB7A865ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5BEA3A-2316-43D3-997C-D36CCE88438C}"/>
+  <xr:revisionPtr revIDLastSave="1121" documentId="11_F25DC773A252ABDACC10482FB9DB7A865ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD39810-E8D1-40CA-A252-7B7B124F1C24}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="232">
   <si>
     <t>session_19_250923_EPA_IntroDays_Overasselt</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>Q_Role_Faculty_Other</t>
+  </si>
+  <si>
+    <t>RiskPerception_6</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -786,6 +789,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -799,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -827,6 +836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1511,6 +1521,9 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>231</v>
+      </c>
       <c r="B23" t="s">
         <v>98</v>
       </c>
@@ -2364,9 +2377,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="A19" t="str">
         <f>+Overview!A23</f>
-        <v>0</v>
+        <v>RiskPerception_6</v>
       </c>
       <c r="B19" t="str">
         <f>+Overview!B23</f>
@@ -3457,9 +3470,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="A19" t="str">
         <f>+Overview!A23</f>
-        <v>0</v>
+        <v>RiskPerception_6</v>
       </c>
       <c r="B19" t="str">
         <f>+Overview!B23</f>
@@ -4468,9 +4481,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="A19" t="str">
         <f>+Overview!A23</f>
-        <v>0</v>
+        <v>RiskPerception_6</v>
       </c>
       <c r="B19" t="str">
         <f>+Overview!B23</f>

--- a/Datasets/vjcortesa_Presurvey_questions overview.xlsx
+++ b/Datasets/vjcortesa_Presurvey_questions overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/jcortesarevalo_tudelft_nl/Documents/Documents/TUDelft/18_Game Data Analysis/R data analysis BEPs/Datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/idattatreya_tudelft_nl/Documents/BEP/BranchInes/Datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1117" documentId="11_F25DC773A252ABDACC10482FB9DB7A865ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5BEA3A-2316-43D3-997C-D36CCE88438C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="18426" windowHeight="11746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1109,14 +1109,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F56BA4-B522-4F82-B63C-985A4FECC66C}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="40.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.29296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.05859375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="40.52734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>213</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>214</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>215</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>216</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B6" t="s">
         <v>113</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>2) What is the highest level of education you have completed?</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B7" t="s">
         <v>116</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
         <v>115</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B9" t="s">
         <v>230</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>218</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>219</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>220</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>221</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
         <v>222</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>223</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>224</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>225</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>226</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A19" s="3"/>
       <c r="B19" t="s">
         <v>94</v>
@@ -1453,7 +1453,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
         <v>227</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>228</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
         <v>229</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="B23" t="s">
         <v>98</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="43" x14ac:dyDescent="0.5">
       <c r="B24" t="s">
         <v>99</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B25" t="s">
         <v>100</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B26" t="s">
         <v>101</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B27" t="s">
         <v>102</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="57.35" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
         <v>103</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B29" t="s">
         <v>104</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B30" t="s">
         <v>105</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B31" t="s">
         <v>106</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B32" t="s">
         <v>107</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B33" t="s">
         <v>108</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B34" t="s">
         <v>109</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B35" t="s">
         <v>110</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B36" t="s">
         <v>114</v>
       </c>
@@ -1736,23 +1736,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA5D072-F21D-421D-B20F-3E70CE670902}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.6328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="40.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.8203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.52734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.29296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.64453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.52734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.46875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>213</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
         <f>+Overview!A2</f>
         <v>Presurvey_id-0-1</v>
@@ -1809,7 +1809,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
         <f>+Overview!A3</f>
         <v>Presurvey_id-0-2</v>
@@ -1828,7 +1828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="43" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
         <f>+Overview!A4</f>
         <v>Presurvey_id-0-3</v>
@@ -1853,7 +1853,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
         <f>+Overview!A5</f>
         <v>Presurvey_id-0-4</v>
@@ -1872,7 +1872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A6">
         <f>+Overview!A8</f>
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A7">
         <f>+Overview!A9</f>
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A8" t="str">
         <f>+Overview!A10</f>
         <v>RiskPerception_1</v>
@@ -1960,7 +1960,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A9" t="str">
         <f>+Overview!A12</f>
         <v>RiskPerception_2_1</v>
@@ -1997,7 +1997,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A10" t="str">
         <f>+Overview!A13</f>
         <v>RiskPerception_2_2</v>
@@ -2041,7 +2041,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A11" t="str">
         <f>+Overview!A14</f>
         <v>RiskPerception_2_3</v>
@@ -2085,7 +2085,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A12" t="str">
         <f>+Overview!A15</f>
         <v>RiskPerception_2_4</v>
@@ -2129,7 +2129,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A13" t="str">
         <f>+Overview!A16</f>
         <v>RiskPerception_2_5</v>
@@ -2173,7 +2173,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A14" t="str">
         <f>+Overview!A17</f>
         <v>RiskPerception_2_6</v>
@@ -2217,7 +2217,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A15" t="str">
         <f>+Overview!A18</f>
         <v>RiskPerception_2_7</v>
@@ -2261,7 +2261,7 @@
         <v>6 = Eén keer per dag</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A16" t="str">
         <f>+Overview!A20</f>
         <v>RiskPerception_3</v>
@@ -2295,7 +2295,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A17" t="str">
         <f>+Overview!A21</f>
         <v>RiskPerception_4</v>
@@ -2329,7 +2329,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" t="str">
         <f>+Overview!A22</f>
         <v>RiskPerception_5</v>
@@ -2363,7 +2363,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="43" x14ac:dyDescent="0.5">
       <c r="A19">
         <f>+Overview!A23</f>
         <v>0</v>
@@ -2397,7 +2397,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A20">
         <f>+Overview!A25</f>
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A21">
         <f>+Overview!A26</f>
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>6 = Ik weet het niet</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A22">
         <f>+Overview!A27</f>
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>6 = Ik weet het niet</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="43" x14ac:dyDescent="0.5">
       <c r="A23">
         <f>+Overview!A28</f>
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A24">
         <f>+Overview!A29</f>
         <v>0</v>
@@ -2605,7 +2605,7 @@
       <c r="L24" s="10"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A25">
         <f>+Overview!A30</f>
         <v>0</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L25" s="10"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A26">
         <f>+Overview!A31</f>
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L26" s="10"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A27">
         <f>+Overview!A32</f>
         <v>0</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="L27" s="10"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A28">
         <f>+Overview!A33</f>
         <v>0</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="L28" s="10"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A29">
         <f>+Overview!A34</f>
         <v>0</v>
@@ -2839,23 +2839,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DCD124A-064F-4E6B-8218-777D01B92C7A}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.8203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.52734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.29296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.52734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.17578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.46875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>213</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
         <f>+Overview!A2</f>
         <v>Presurvey_id-0-1</v>
@@ -2912,7 +2912,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
         <f>+Overview!A3</f>
         <v>Presurvey_id-0-2</v>
@@ -2931,7 +2931,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
         <f>+Overview!A4</f>
         <v>Presurvey_id-0-3</v>
@@ -2956,7 +2956,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
         <f>+Overview!A5</f>
         <v>Presurvey_id-0-4</v>
@@ -2975,7 +2975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A6">
         <f>+Overview!A8</f>
         <v>0</v>
@@ -2994,7 +2994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A7" t="str">
         <f>+Overview!A10</f>
         <v>RiskPerception_1</v>
@@ -3028,7 +3028,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A8" t="str">
         <f>+Overview!A12</f>
         <v>RiskPerception_2_1</v>
@@ -3065,7 +3065,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A9" t="str">
         <f>+Overview!A13</f>
         <v>RiskPerception_2_2</v>
@@ -3109,7 +3109,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A10" t="str">
         <f>+Overview!A14</f>
         <v>RiskPerception_2_3</v>
@@ -3153,7 +3153,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A11" t="str">
         <f>+Overview!A15</f>
         <v>RiskPerception_2_4</v>
@@ -3197,7 +3197,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A12" t="str">
         <f>+Overview!A16</f>
         <v>RiskPerception_2_5</v>
@@ -3241,7 +3241,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A13" t="str">
         <f>+Overview!A17</f>
         <v>RiskPerception_2_6</v>
@@ -3285,7 +3285,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A14" t="str">
         <f>+Overview!A18</f>
         <v>RiskPerception_2_7</v>
@@ -3329,7 +3329,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="43" x14ac:dyDescent="0.5">
       <c r="A15">
         <f>+Overview!A19</f>
         <v>0</v>
@@ -3354,7 +3354,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A16" t="str">
         <f>+Overview!A20</f>
         <v>RiskPerception_3</v>
@@ -3388,7 +3388,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="43" x14ac:dyDescent="0.5">
       <c r="A17" t="str">
         <f>+Overview!A21</f>
         <v>RiskPerception_4</v>
@@ -3422,7 +3422,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" t="str">
         <f>+Overview!A22</f>
         <v>RiskPerception_5</v>
@@ -3456,7 +3456,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A19">
         <f>+Overview!A23</f>
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A20">
         <f>+Overview!A25</f>
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A21">
         <f>+Overview!A26</f>
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>6 = I don't know</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A22">
         <f>+Overview!A27</f>
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>6 = I don't know</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A23">
         <f>+Overview!A29</f>
         <v>0</v>
@@ -3654,7 +3654,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A24">
         <f>+Overview!A30</f>
         <v>0</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A25">
         <f>+Overview!A31</f>
         <v>0</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A26">
         <f>+Overview!A32</f>
         <v>0</v>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A27">
         <f>+Overview!A33</f>
         <v>0</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A28">
         <f>+Overview!A34</f>
         <v>0</v>
@@ -3888,23 +3888,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.8203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.52734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.29296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.17578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.52734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.17578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.46875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>213</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A2" t="str">
         <f>+Overview!A2</f>
         <v>Presurvey_id-0-1</v>
@@ -3961,7 +3961,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" t="str">
         <f>+Overview!A3</f>
         <v>Presurvey_id-0-2</v>
@@ -3980,7 +3980,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
         <f>+Overview!A4</f>
         <v>Presurvey_id-0-3</v>
@@ -4005,7 +4005,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
         <f>+Overview!A5</f>
         <v>Presurvey_id-0-4</v>
@@ -4024,7 +4024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A6">
         <f>+Overview!A6</f>
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A7">
         <f>+Overview!A8</f>
         <v>0</v>
@@ -4074,7 +4074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A8">
         <f>+Overview!A9</f>
         <v>0</v>
@@ -4093,7 +4093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A9" t="str">
         <f>+Overview!A10</f>
         <v>RiskPerception_1</v>
@@ -4127,7 +4127,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A10" t="str">
         <f>+Overview!A12</f>
         <v>RiskPerception_2_1</v>
@@ -4164,7 +4164,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A11" t="str">
         <f>+Overview!A13</f>
         <v>RiskPerception_2_2</v>
@@ -4208,7 +4208,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A12" t="str">
         <f>+Overview!A14</f>
         <v>RiskPerception_2_3</v>
@@ -4252,7 +4252,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A13" t="str">
         <f>+Overview!A15</f>
         <v>RiskPerception_2_4</v>
@@ -4296,7 +4296,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A14" t="str">
         <f>+Overview!A16</f>
         <v>RiskPerception_2_5</v>
@@ -4340,7 +4340,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="43" x14ac:dyDescent="0.5">
       <c r="A15">
         <f>+Overview!A19</f>
         <v>0</v>
@@ -4365,7 +4365,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A16" t="str">
         <f>+Overview!A20</f>
         <v>RiskPerception_3</v>
@@ -4399,7 +4399,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="43" x14ac:dyDescent="0.5">
       <c r="A17" t="str">
         <f>+Overview!A21</f>
         <v>RiskPerception_4</v>
@@ -4433,7 +4433,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" t="str">
         <f>+Overview!A22</f>
         <v>RiskPerception_5</v>
@@ -4467,7 +4467,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A19">
         <f>+Overview!A23</f>
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A20">
         <f>+Overview!A25</f>
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A21">
         <f>+Overview!A26</f>
         <v>0</v>
@@ -4582,7 +4582,7 @@
         <v>6 = I don't know</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A22">
         <f>+Overview!A27</f>
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>6 = I don't know</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A23">
         <f>+Overview!A29</f>
         <v>0</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24">
         <f>+Overview!A30</f>
         <v>0</v>
@@ -4715,7 +4715,7 @@
         <v>7 = None, I dont' know</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A25">
         <f>+Overview!A31</f>
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>7 = None, I dont' know</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A26">
         <f>+Overview!A32</f>
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>7 = None, I dont' know</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A27">
         <f>+Overview!A33</f>
         <v>0</v>
@@ -4859,7 +4859,7 @@
         <v>7 = None, I dont' know</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A28">
         <f>+Overview!A34</f>
         <v>0</v>
@@ -4907,7 +4907,7 @@
         <v>7 = None, I dont' know</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A29">
         <f>+Overview!A35</f>
         <v>0</v>
